--- a/historico_gcpec.xlsx
+++ b/historico_gcpec.xlsx
@@ -24,32 +24,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Execucao_DataHora | DEPARTAMENTO | Status_PEC</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:00:00 | FARMÁCIA CENTRAL | FALTA AUTOAVALIAÇÃO</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:05:00 | UTI GERAL | FALTA REGISTRO DO CONSENSO</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:10:00 | UNIDADE DE INTERNAÇÃO | FALTA AUTOAVALIAÇÃO</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:15:00 | EMERGÊNCIA | FALTA AVALIAÇÃO DO GESTOR</t>
-  </si>
-  <si>
-    <t>2026-03-20 09:20:00 | CENTRO CIRÚRGICO | FALTA AUTOAVALIAÇÃO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+  <si>
+    <t>Status_Pendencia</t>
+  </si>
+  <si>
+    <t>Execucao_DataHora</t>
+  </si>
+  <si>
+    <t>FARMÁCIA CENTRAL</t>
+  </si>
+  <si>
+    <t>FALTA AUTOAVALIAÇÃO</t>
+  </si>
+  <si>
+    <t>UTI GERAL</t>
+  </si>
+  <si>
+    <t>FALTA REGISTRO DO CONSENSO</t>
+  </si>
+  <si>
+    <t>UNIDADE DE INTERNAÇÃO</t>
+  </si>
+  <si>
+    <t>EMERGÊNCIA</t>
+  </si>
+  <si>
+    <t>FALTA AVALIAÇÃO DO GESTOR</t>
+  </si>
+  <si>
+    <t>CENTRO CIRÚRGICO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -77,8 +97,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,38 +388,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>46101.375</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46101.378472222219</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46101.381944444445</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46101.385416666664</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46101.388888888891</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
